--- a/data/Store_Master.xlsx
+++ b/data/Store_Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/FB-Sales/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{DB8E79A2-F353-468B-8FC9-094421811B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F430BBF-CD67-428E-97E8-CD89C612751A}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{DB8E79A2-F353-468B-8FC9-094421811B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{713A1FF7-B608-48C6-8E82-7C2A6FDD2965}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7D4174F8-86A5-4506-B54F-CFAB4FB5A869}"/>
   </bookViews>
@@ -759,9 +759,6 @@
     <t>MCC AL MAJAZ</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>store_sr_no</t>
   </si>
   <si>
@@ -787,6 +784,9 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>Active</t>
   </si>
 </sst>
 </file>
@@ -1160,31 +1160,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -1207,7 +1207,7 @@
         <v>229</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H2" s="1">
         <v>6101026855</v>
@@ -1236,7 +1236,7 @@
         <v>229</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H3" s="1">
         <v>6101027080</v>
@@ -1265,7 +1265,7 @@
         <v>229</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H4" s="1">
         <v>6101336857</v>
@@ -1294,7 +1294,7 @@
         <v>229</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H5" s="1">
         <v>6101043251</v>
@@ -1323,7 +1323,7 @@
         <v>229</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H6" s="1">
         <v>6101245019</v>
@@ -1352,7 +1352,7 @@
         <v>229</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H7" s="1">
         <v>6101246409</v>
@@ -1381,7 +1381,7 @@
         <v>229</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H8" s="1">
         <v>6101246811</v>
@@ -1410,7 +1410,7 @@
         <v>229</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H9" s="1">
         <v>6101046856</v>
@@ -1439,7 +1439,7 @@
         <v>229</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H10" s="1">
         <v>6101047034</v>
@@ -1468,7 +1468,7 @@
         <v>229</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H11" s="1">
         <v>6101063273</v>
@@ -1497,7 +1497,7 @@
         <v>229</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H12" s="1">
         <v>6101174581</v>
@@ -1526,7 +1526,7 @@
         <v>229</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H13" s="1">
         <v>6101083292</v>
@@ -1555,7 +1555,7 @@
         <v>230</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H14" s="1">
         <v>3101316894</v>
@@ -1584,7 +1584,7 @@
         <v>230</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H15" s="1">
         <v>3101417382</v>
@@ -1613,7 +1613,7 @@
         <v>230</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H16" s="1">
         <v>3101027352</v>
@@ -1642,7 +1642,7 @@
         <v>230</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H17" s="1">
         <v>3101437288</v>
@@ -1671,7 +1671,7 @@
         <v>230</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H18" s="1">
         <v>3101437297</v>
@@ -1700,7 +1700,7 @@
         <v>230</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H19" s="1">
         <v>3101046975</v>
@@ -1729,7 +1729,7 @@
         <v>230</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H20" s="1">
         <v>3101156803</v>
@@ -1758,7 +1758,7 @@
         <v>230</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H21" s="1">
         <v>3101376517</v>
@@ -1787,7 +1787,7 @@
         <v>230</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H22" s="1">
         <v>3101376885</v>
@@ -1816,7 +1816,7 @@
         <v>230</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H23" s="1">
         <v>3101376886</v>
@@ -1845,7 +1845,7 @@
         <v>230</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H24" s="1">
         <v>3101276971</v>
@@ -1874,7 +1874,7 @@
         <v>230</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H25" s="1">
         <v>3101276972</v>
@@ -1903,7 +1903,7 @@
         <v>230</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H26" s="1">
         <v>3101276980</v>
@@ -1932,7 +1932,7 @@
         <v>230</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H27" s="1">
         <v>3101277289</v>
@@ -1961,7 +1961,7 @@
         <v>230</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H28" s="1">
         <v>3101377353</v>
@@ -1990,7 +1990,7 @@
         <v>230</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H29" s="1">
         <v>3101377354</v>
@@ -2019,7 +2019,7 @@
         <v>230</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H30" s="1">
         <v>3101396789</v>
@@ -2048,7 +2048,7 @@
         <v>231</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H31" s="1">
         <v>5101315524</v>
@@ -2077,7 +2077,7 @@
         <v>231</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H32" s="1">
         <v>5101315920</v>
@@ -2106,7 +2106,7 @@
         <v>231</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H33" s="1">
         <v>5101526589</v>
@@ -2135,7 +2135,7 @@
         <v>231</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H34" s="1">
         <v>5101103133</v>
@@ -2164,7 +2164,7 @@
         <v>231</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H35" s="1">
         <v>5101133161</v>
@@ -2193,7 +2193,7 @@
         <v>231</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H36" s="1">
         <v>5101135842</v>
@@ -2222,7 +2222,7 @@
         <v>231</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H37" s="1">
         <v>5101045507</v>
@@ -2251,7 +2251,7 @@
         <v>231</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H38" s="1">
         <v>5101045041</v>
@@ -2280,7 +2280,7 @@
         <v>231</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H39" s="1">
         <v>5101045552</v>
@@ -2309,7 +2309,7 @@
         <v>231</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H40" s="1">
         <v>5101355846</v>
@@ -2338,7 +2338,7 @@
         <v>231</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H41" s="1">
         <v>5101163673</v>
@@ -2367,7 +2367,7 @@
         <v>231</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H42" s="1">
         <v>5101164140</v>
@@ -2396,7 +2396,7 @@
         <v>231</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H43" s="1">
         <v>5101164768</v>
@@ -2425,7 +2425,7 @@
         <v>231</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H44" s="1">
         <v>5101165841</v>
@@ -2454,7 +2454,7 @@
         <v>231</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H45" s="1">
         <v>5101073103</v>
@@ -2483,7 +2483,7 @@
         <v>231</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H46" s="1">
         <v>5101173780</v>
@@ -2512,7 +2512,7 @@
         <v>231</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H47" s="1">
         <v>5101095308</v>
@@ -2541,7 +2541,7 @@
         <v>231</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H48" s="1">
         <v>5101295502</v>
@@ -2570,7 +2570,7 @@
         <v>231</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H49" s="1">
         <v>5101295503</v>
@@ -2599,7 +2599,7 @@
         <v>231</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H50" s="1">
         <v>5101095891</v>
@@ -2628,7 +2628,7 @@
         <v>232</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H51" s="1">
         <v>2271116119</v>
@@ -2657,7 +2657,7 @@
         <v>232</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H52" s="1">
         <v>2181516847</v>
@@ -2686,7 +2686,7 @@
         <v>232</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H53" s="1">
         <v>2181517313</v>
@@ -2715,7 +2715,7 @@
         <v>232</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H54" s="1">
         <v>2181817332</v>
@@ -2744,7 +2744,7 @@
         <v>232</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H55" s="1">
         <v>2271817368</v>
@@ -2773,7 +2773,7 @@
         <v>232</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H56" s="1">
         <v>2271817369</v>
@@ -2802,7 +2802,7 @@
         <v>232</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H57" s="1">
         <v>2271826334</v>
@@ -2831,7 +2831,7 @@
         <v>232</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H58" s="1">
         <v>2272226649</v>
@@ -2860,7 +2860,7 @@
         <v>232</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H59" s="1">
         <v>2271226731</v>
@@ -2889,7 +2889,7 @@
         <v>232</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H60" s="1">
         <v>2271126872</v>
@@ -2918,7 +2918,7 @@
         <v>232</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H61" s="1">
         <v>2271627075</v>
@@ -2947,7 +2947,7 @@
         <v>232</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H62" s="1">
         <v>2272427108</v>
@@ -2976,7 +2976,7 @@
         <v>232</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H63" s="1">
         <v>2272427109</v>
@@ -3005,7 +3005,7 @@
         <v>232</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H64" s="1">
         <v>2272427166</v>
@@ -3034,7 +3034,7 @@
         <v>232</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H65" s="1">
         <v>2272427167</v>
@@ -3063,7 +3063,7 @@
         <v>232</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H66" s="1">
         <v>2271127169</v>
@@ -3092,7 +3092,7 @@
         <v>232</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H67" s="1">
         <v>2271627220</v>
@@ -3121,7 +3121,7 @@
         <v>232</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H68" s="1">
         <v>2271627247</v>
@@ -3150,7 +3150,7 @@
         <v>232</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H69" s="1">
         <v>2271127291</v>
@@ -3179,7 +3179,7 @@
         <v>232</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H70" s="1">
         <v>2221227313</v>
@@ -3208,7 +3208,7 @@
         <v>232</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H71" s="1">
         <v>2272527392</v>
@@ -3237,7 +3237,7 @@
         <v>232</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H72" s="1">
         <v>2271035438</v>
@@ -3266,7 +3266,7 @@
         <v>232</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H73" s="1">
         <v>2271035439</v>
@@ -3295,7 +3295,7 @@
         <v>232</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H74" s="1">
         <v>2272136292</v>
@@ -3324,7 +3324,7 @@
         <v>232</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H75" s="1">
         <v>2271306413</v>
@@ -3353,7 +3353,7 @@
         <v>232</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H76" s="1">
         <v>2231036674</v>
@@ -3382,7 +3382,7 @@
         <v>232</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H77" s="1">
         <v>2181736678</v>
@@ -3411,7 +3411,7 @@
         <v>232</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H78" s="1">
         <v>2181736679</v>
@@ -3440,7 +3440,7 @@
         <v>232</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H79" s="1">
         <v>2271306797</v>
@@ -3469,7 +3469,7 @@
         <v>232</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H80" s="1">
         <v>2271036871</v>
@@ -3498,7 +3498,7 @@
         <v>232</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H81" s="1">
         <v>2271307072</v>
@@ -3527,7 +3527,7 @@
         <v>232</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H82" s="1">
         <v>2181737116</v>
@@ -3556,7 +3556,7 @@
         <v>232</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H83" s="1">
         <v>2271037241</v>
@@ -3585,7 +3585,7 @@
         <v>232</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H84" s="1">
         <v>2221237420</v>
@@ -3614,7 +3614,7 @@
         <v>232</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H85" s="1">
         <v>2271645857</v>
@@ -3643,7 +3643,7 @@
         <v>232</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H86" s="1">
         <v>2271646295</v>
@@ -3672,7 +3672,7 @@
         <v>232</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H87" s="1">
         <v>2272146732</v>
@@ -3701,7 +3701,7 @@
         <v>232</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H88" s="1">
         <v>2271747425</v>
@@ -3730,7 +3730,7 @@
         <v>232</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H89" s="1">
         <v>2271152654</v>
@@ -3759,7 +3759,7 @@
         <v>232</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H90" s="1">
         <v>2271256414</v>
@@ -3788,7 +3788,7 @@
         <v>232</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H91" s="1">
         <v>2271056543</v>
@@ -3817,7 +3817,7 @@
         <v>232</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H92" s="1">
         <v>2271356826</v>
@@ -3846,7 +3846,7 @@
         <v>232</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H93" s="1">
         <v>2181756874</v>
@@ -3875,7 +3875,7 @@
         <v>232</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H94" s="1">
         <v>2231057430</v>
@@ -3904,7 +3904,7 @@
         <v>232</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H95" s="1">
         <v>2231057431</v>
@@ -3933,7 +3933,7 @@
         <v>232</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H96" s="1">
         <v>2231057432</v>
@@ -3962,7 +3962,7 @@
         <v>232</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H97" s="1">
         <v>2151164995</v>
@@ -3991,7 +3991,7 @@
         <v>232</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H98" s="1">
         <v>2151164996</v>
@@ -4020,7 +4020,7 @@
         <v>232</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H99" s="1">
         <v>2151166876</v>
@@ -4049,7 +4049,7 @@
         <v>232</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H100" s="1">
         <v>2272367037</v>
@@ -4078,7 +4078,7 @@
         <v>232</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H101" s="1">
         <v>2221167091</v>
@@ -4107,7 +4107,7 @@
         <v>232</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H102" s="1">
         <v>2272367126</v>
@@ -4136,7 +4136,7 @@
         <v>232</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H103" s="1">
         <v>2271167242</v>
@@ -4165,7 +4165,7 @@
         <v>232</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H104" s="1">
         <v>2272467251</v>
@@ -4194,7 +4194,7 @@
         <v>232</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H105" s="1">
         <v>2272467255</v>
@@ -4223,7 +4223,7 @@
         <v>232</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H106" s="1">
         <v>2181767257</v>
@@ -4252,7 +4252,7 @@
         <v>232</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H107" s="1">
         <v>2181767258</v>
@@ -4281,7 +4281,7 @@
         <v>232</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H108" s="1">
         <v>2181767259</v>
@@ -4310,7 +4310,7 @@
         <v>232</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H109" s="1">
         <v>2181767260</v>
@@ -4339,7 +4339,7 @@
         <v>232</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H110" s="1">
         <v>2181767261</v>
@@ -4368,7 +4368,7 @@
         <v>232</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H111" s="1">
         <v>2272467280</v>
@@ -4397,7 +4397,7 @@
         <v>232</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H112" s="1">
         <v>2231167391</v>
@@ -4426,7 +4426,7 @@
         <v>232</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H113" s="1">
         <v>2272567421</v>
@@ -4455,7 +4455,7 @@
         <v>232</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H114" s="1">
         <v>2272567422</v>
@@ -4484,7 +4484,7 @@
         <v>232</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H115" s="1">
         <v>2271875679</v>
@@ -4513,7 +4513,7 @@
         <v>232</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H116" s="1">
         <v>2271875839</v>
@@ -4542,7 +4542,7 @@
         <v>232</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H117" s="1">
         <v>2271875840</v>
@@ -4571,7 +4571,7 @@
         <v>232</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H118" s="1">
         <v>2271976291</v>
@@ -4600,7 +4600,7 @@
         <v>232</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H119" s="1">
         <v>2181276354</v>
@@ -4629,7 +4629,7 @@
         <v>232</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H120" s="1">
         <v>2271876873</v>
@@ -4658,7 +4658,7 @@
         <v>232</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H121" s="1">
         <v>2181276875</v>
@@ -4687,7 +4687,7 @@
         <v>232</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H122" s="1">
         <v>2271876948</v>
@@ -4716,7 +4716,7 @@
         <v>232</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H123" s="1">
         <v>2272377042</v>
@@ -4745,7 +4745,7 @@
         <v>232</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H124" s="1">
         <v>2181577093</v>
@@ -4774,7 +4774,7 @@
         <v>232</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H125" s="1">
         <v>2181777267</v>
@@ -4803,7 +4803,7 @@
         <v>232</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H126" s="1">
         <v>2272477311</v>
@@ -4832,7 +4832,7 @@
         <v>232</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H127" s="1">
         <v>2181277329</v>
@@ -4861,7 +4861,7 @@
         <v>232</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H128" s="1">
         <v>2201077343</v>
@@ -4890,7 +4890,7 @@
         <v>232</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H129" s="1">
         <v>2201077418</v>
@@ -4919,7 +4919,7 @@
         <v>232</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H130" s="1">
         <v>2181787275</v>
@@ -4948,7 +4948,7 @@
         <v>232</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H131" s="1">
         <v>2272487312</v>
@@ -4977,7 +4977,7 @@
         <v>232</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H132" s="1">
         <v>2151287330</v>
@@ -5006,7 +5006,7 @@
         <v>232</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H133" s="1">
         <v>2271687493</v>
@@ -5035,7 +5035,7 @@
         <v>232</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H134" s="1">
         <v>2271687494</v>
@@ -5064,7 +5064,7 @@
         <v>232</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H135" s="1">
         <v>2271687504</v>
@@ -5093,7 +5093,7 @@
         <v>232</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H136" s="1">
         <v>2272497331</v>
@@ -5122,7 +5122,7 @@
         <v>232</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H137" s="1">
         <v>2272497423</v>
@@ -5151,7 +5151,7 @@
         <v>232</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H138" s="1">
         <v>2272497424</v>
@@ -5180,7 +5180,7 @@
         <v>233</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H139" s="1">
         <v>1131305742</v>
@@ -5209,7 +5209,7 @@
         <v>233</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H140" s="1">
         <v>1131835791</v>
@@ -5238,7 +5238,7 @@
         <v>233</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H141" s="1">
         <v>1131764960</v>
@@ -5267,7 +5267,7 @@
         <v>233</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H142" s="1">
         <v>1101011010</v>
@@ -5296,7 +5296,7 @@
         <v>233</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H143" s="1">
         <v>1131611935</v>
@@ -5325,7 +5325,7 @@
         <v>233</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H144" s="1">
         <v>1141012033</v>
@@ -5354,7 +5354,7 @@
         <v>233</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H145" s="1">
         <v>1161012156</v>
@@ -5383,7 +5383,7 @@
         <v>233</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H146" s="1">
         <v>1131916146</v>
@@ -5412,7 +5412,7 @@
         <v>233</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H147" s="1">
         <v>1131916193</v>
@@ -5441,7 +5441,7 @@
         <v>233</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H148" s="1">
         <v>1131916194</v>
@@ -5470,7 +5470,7 @@
         <v>233</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H149" s="1">
         <v>1131016512</v>
@@ -5499,7 +5499,7 @@
         <v>233</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H150" s="1">
         <v>1132016542</v>
@@ -5528,7 +5528,7 @@
         <v>233</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H151" s="1">
         <v>1132116991</v>
@@ -5557,7 +5557,7 @@
         <v>233</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H152" s="1">
         <v>1171022215</v>
@@ -5586,7 +5586,7 @@
         <v>233</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H153" s="1">
         <v>1101124586</v>
@@ -5615,7 +5615,7 @@
         <v>233</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H154" s="1">
         <v>1101124587</v>
@@ -5644,7 +5644,7 @@
         <v>233</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H155" s="1">
         <v>1101425844</v>
@@ -5673,7 +5673,7 @@
         <v>233</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H156" s="1">
         <v>1111025924</v>
@@ -5702,7 +5702,7 @@
         <v>233</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H157" s="1">
         <v>1101426569</v>
@@ -5731,7 +5731,7 @@
         <v>233</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H158" s="1">
         <v>1101126573</v>
@@ -5760,7 +5760,7 @@
         <v>233</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H159" s="1">
         <v>1101426685</v>
@@ -5789,7 +5789,7 @@
         <v>233</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H160" s="1">
         <v>1101327008</v>
@@ -5818,7 +5818,7 @@
         <v>233</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H161" s="1">
         <v>1131431821</v>
@@ -5847,7 +5847,7 @@
         <v>233</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H162" s="1">
         <v>1161032176</v>
@@ -5876,7 +5876,7 @@
         <v>233</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H163" s="1">
         <v>1131835789</v>
@@ -5905,7 +5905,7 @@
         <v>233</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H164" s="1">
         <v>1131835790</v>
@@ -5934,7 +5934,7 @@
         <v>233</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H165" s="1">
         <v>1131835792</v>
@@ -5963,7 +5963,7 @@
         <v>233</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H166" s="1">
         <v>1131835874</v>
@@ -5992,7 +5992,7 @@
         <v>233</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H167" s="1">
         <v>1131136204</v>
@@ -6021,7 +6021,7 @@
         <v>233</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H168" s="1">
         <v>1101436374</v>
@@ -6050,7 +6050,7 @@
         <v>233</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H169" s="1">
         <v>1101241176</v>
@@ -6079,7 +6079,7 @@
         <v>233</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H170" s="1">
         <v>1111041236</v>
@@ -6108,7 +6108,7 @@
         <v>233</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H171" s="1">
         <v>1131341759</v>
@@ -6137,7 +6137,7 @@
         <v>233</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H172" s="1">
         <v>1131304336</v>
@@ -6166,7 +6166,7 @@
         <v>233</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H173" s="1">
         <v>1131846723</v>
@@ -6195,7 +6195,7 @@
         <v>233</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H174" s="1">
         <v>1131151593</v>
@@ -6224,7 +6224,7 @@
         <v>233</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H175" s="1">
         <v>1121054515</v>
@@ -6253,7 +6253,7 @@
         <v>233</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H176" s="1">
         <v>1121054516</v>
@@ -6282,7 +6282,7 @@
         <v>233</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H177" s="1">
         <v>1131856145</v>
@@ -6311,7 +6311,7 @@
         <v>233</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H178" s="1">
         <v>1121056722</v>
@@ -6340,7 +6340,7 @@
         <v>233</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H179" s="1">
         <v>1101456822</v>
@@ -6369,7 +6369,7 @@
         <v>233</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H180" s="1">
         <v>1101456823</v>
@@ -6398,7 +6398,7 @@
         <v>233</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H181" s="1">
         <v>1101457286</v>
@@ -6427,7 +6427,7 @@
         <v>233</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H182" s="1">
         <v>1131261725</v>
@@ -6456,7 +6456,7 @@
         <v>233</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H183" s="1">
         <v>1131361771</v>
@@ -6485,7 +6485,7 @@
         <v>233</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H184" s="1">
         <v>1131264753</v>
@@ -6514,7 +6514,7 @@
         <v>233</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H185" s="1">
         <v>1161066526</v>
@@ -6543,7 +6543,7 @@
         <v>233</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H186" s="1">
         <v>1161066527</v>
@@ -6572,7 +6572,7 @@
         <v>233</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H187" s="1">
         <v>1131366724</v>
@@ -6601,7 +6601,7 @@
         <v>233</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H188" s="1">
         <v>1161066735</v>
@@ -6630,7 +6630,7 @@
         <v>233</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H189" s="1">
         <v>1101466896</v>
@@ -6659,7 +6659,7 @@
         <v>233</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H190" s="1">
         <v>1131267032</v>
@@ -6688,7 +6688,7 @@
         <v>233</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H191" s="1">
         <v>1141067033</v>
@@ -6717,7 +6717,7 @@
         <v>233</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H192" s="1">
         <v>1131071340</v>
@@ -6746,7 +6746,7 @@
         <v>233</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H193" s="1">
         <v>1131471852</v>
@@ -6775,7 +6775,7 @@
         <v>233</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H194" s="1">
         <v>1131081352</v>
@@ -6804,7 +6804,7 @@
         <v>233</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H195" s="1">
         <v>1131181630</v>
@@ -6833,7 +6833,7 @@
         <v>233</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H196" s="1">
         <v>1131185785</v>
@@ -6862,7 +6862,7 @@
         <v>233</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H197" s="1">
         <v>1132086787</v>
@@ -6891,7 +6891,7 @@
         <v>233</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H198" s="1">
         <v>1131287152</v>
@@ -6920,7 +6920,7 @@
         <v>233</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H199" s="1">
         <v>1131887268</v>
@@ -6949,7 +6949,7 @@
         <v>233</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H200" s="1">
         <v>1101487389</v>
@@ -6978,7 +6978,7 @@
         <v>233</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H201" s="1">
         <v>1131487482</v>
@@ -7007,7 +7007,7 @@
         <v>233</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H202" s="1">
         <v>1101091055</v>
@@ -7036,7 +7036,7 @@
         <v>233</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H203" s="1">
         <v>1131191672</v>
@@ -7065,7 +7065,7 @@
         <v>233</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H204" s="1">
         <v>1131391800</v>
@@ -7094,7 +7094,7 @@
         <v>233</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H205" s="1">
         <v>1171092294</v>
@@ -7123,7 +7123,7 @@
         <v>233</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H206" s="1">
         <v>1171094514</v>
@@ -7152,7 +7152,7 @@
         <v>233</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H207" s="1">
         <v>1131795870</v>
@@ -7181,7 +7181,7 @@
         <v>233</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H208" s="1">
         <v>1101295896</v>
@@ -7210,7 +7210,7 @@
         <v>233</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H209" s="1">
         <v>1132096824</v>
@@ -7239,7 +7239,7 @@
         <v>234</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H210" s="1">
         <v>4101416315</v>
@@ -7268,7 +7268,7 @@
         <v>234</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H211" s="1">
         <v>4101416318</v>
@@ -7297,7 +7297,7 @@
         <v>234</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H212" s="1">
         <v>4101416351</v>
@@ -7326,7 +7326,7 @@
         <v>234</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H213" s="1">
         <v>4101316940</v>
@@ -7355,7 +7355,7 @@
         <v>234</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H214" s="1">
         <v>4101517194</v>
@@ -7384,7 +7384,7 @@
         <v>234</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H215" s="1">
         <v>4101527284</v>
@@ -7413,7 +7413,7 @@
         <v>234</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H216" s="1">
         <v>4101527340</v>
@@ -7442,7 +7442,7 @@
         <v>234</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H217" s="1">
         <v>4101136548</v>
@@ -7471,7 +7471,7 @@
         <v>234</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H218" s="1">
         <v>4101537285</v>
@@ -7500,7 +7500,7 @@
         <v>234</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H219" s="1">
         <v>4101056360</v>
@@ -7529,7 +7529,7 @@
         <v>234</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H220" s="1">
         <v>4101457195</v>
@@ -7558,7 +7558,7 @@
         <v>234</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H221" s="1">
         <v>4101376299</v>
@@ -7587,7 +7587,7 @@
         <v>234</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H222" s="1">
         <v>4101477012</v>
@@ -7616,7 +7616,7 @@
         <v>234</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H223" s="1">
         <v>4101486941</v>
@@ -7645,7 +7645,7 @@
         <v>234</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H224" s="1">
         <v>4101296825</v>
@@ -7674,7 +7674,7 @@
         <v>234</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H225" s="1">
         <v>4101297103</v>
@@ -7703,7 +7703,7 @@
         <v>234</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H226" s="1">
         <v>4101097402</v>
